--- a/docs/Project_Planning/overall.xlsx
+++ b/docs/Project_Planning/overall.xlsx
@@ -9619,6 +9619,62 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="矩形 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="165100" y="1371600"/>
+          <a:ext cx="13728700" cy="5048250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>50165</xdr:colOff>
       <xdr:row>12</xdr:row>

--- a/docs/Project_Planning/overall.xlsx
+++ b/docs/Project_Planning/overall.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Git_doc\Real-Time-Embedded-Programming\docs\Project_Planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57544E11-D6E5-43B9-B529-6BD912D183EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F57F2B-864A-4871-A09E-B7DFF2FDE5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="992" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,7 @@
     <sheet name="开发log" sheetId="11" r:id="rId7"/>
     <sheet name="data" sheetId="13" r:id="rId8"/>
     <sheet name="线程管理_0409" sheetId="14" r:id="rId9"/>
+    <sheet name="线程管理_0409 _eng" sheetId="15" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="235">
   <si>
     <t>Motion学习方面如何配置？</t>
   </si>
@@ -730,6 +731,110 @@
   </si>
   <si>
     <t>_synthesisThread</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Main Loop (Pseudo Thread)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microphone Capture Thread</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Triggered via play(), processes data in the queue into playable audio data, and pushes it to the playback thread for playback</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Processing function: synthesisTask()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Input queue: _textQueue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Output queue: _dataQueue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Triggered by queue data, processes the data and buffers the processed data to the internal speaker unit for playback</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Input queue: _dataQueue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Output: internal PCM processing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Triggered by queue data, passes the queued data to executeMotion() for processing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Input queue: MotionQueue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Triggered by queue data, application-level task processing thread</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Input queue: camera_queue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thread-triggered callback, returns current frame</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Callback trigger: onFrame()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Started directly during construction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Started by calling open() during construction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>At start, a frame transmission pipeline is configured, and a callback is triggered when a frame is detected</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>During destruction, both the cap transmission and frame capture threads are stopped</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Submodules are automatically destroyed when RobotSystem is destructed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>module</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>thread name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>file</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>star</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stop</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>thread core</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -20740,7 +20845,7 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>CogniArm  V1.0</a:t>
+            <a:t>CogniArm  V2.0</a:t>
           </a:r>
           <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
             <a:solidFill>
@@ -21180,6 +21285,432 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A9DC4A-0CC4-4407-A248-561200CE148C}">
+  <dimension ref="B2:AB52"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H6" t="s">
+        <v>137</v>
+      </c>
+      <c r="L6" t="s">
+        <v>138</v>
+      </c>
+      <c r="T6" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z6">
+        <v>3</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="L7" t="s">
+        <v>140</v>
+      </c>
+      <c r="T7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>142</v>
+      </c>
+      <c r="T8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F11" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z12">
+        <v>3</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F17" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z17">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="L20" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="L24" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="L26" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F30" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z30">
+        <v>2</v>
+      </c>
+      <c r="AB30" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="L31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="T33" s="3"/>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F35" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z35">
+        <v>2</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B37" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="T39" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L40" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B44" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B47" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B48" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>

--- a/docs/Project_Planning/overall.xlsx
+++ b/docs/Project_Planning/overall.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Git_doc\Real-Time-Embedded-Programming\docs\Project_Planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F57F2B-864A-4871-A09E-B7DFF2FDE5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE62A17F-E570-4B54-AA78-FDBF9687A702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="992" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="992" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,10 @@
     <sheet name="data" sheetId="13" r:id="rId8"/>
     <sheet name="线程管理_0409" sheetId="14" r:id="rId9"/>
     <sheet name="线程管理_0409 _eng" sheetId="15" r:id="rId10"/>
+    <sheet name="线程管理_0411" sheetId="16" r:id="rId11"/>
+    <sheet name="生命周期控制" sheetId="17" r:id="rId12"/>
+    <sheet name="data (2)" sheetId="18" r:id="rId13"/>
+    <sheet name="Sheet2" sheetId="19" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="264">
   <si>
     <t>Motion学习方面如何配置？</t>
   </si>
@@ -837,12 +841,121 @@
     <t>thread core</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>fix:_stop()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fix:_start()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>昨天上线了第一个版本，使用起来体验并不是很好</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先是接收到异常信息后机器人不断回复，比如我在说中文机器人也不断回复，这样符合要求，应该也追加一个lock</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>其次时检测结果的反馈不是很足</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cam检测到了mic和motion都要有动作就很好</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cam没检测到，或者motion学习失败，或者motion调用了没学过的都需要有反馈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这就需要下级执行者来记录结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>顺便可以记录每一个task完成的事件，来计算一下延迟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时还要改善speaker回复慢的情况，并不是需要时间相应，而是需要时间来处理数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测part需要极度解耦，也就是说我可以单独去掉这个检测p，不影响整个环节的运行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同样的，语言切换得做啊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他模块也最好是这样，启动的时候应该返回一个code，来报告这次启动哪些地方是ok的哪些有问题</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>零延迟优先级最高，先做反馈和延迟记录，再处理speaker，在处理语言问题</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初步想法是单独设计一个模块</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将一个模块注入到每个执行者中，也就是一个指针，这个指针某个位置指向了一个队列。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>然后在各个执行者处进行处理，当任务开始时向队列中push一条任务开始数据，包括任务模块，任务类型，起始时间，任务id，</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>然后在任务结束的时候push进另一条任务数据，分别是任务类型，任务结束时间，任务结果（不同模块结果不同），任务id，</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>然后上级模块设计一个线程来检测这个队列，对id相同的模块进行匹配，计算任务执行时间并将任务执行时间与任务类型写入测试文档中，然后再根据任务结果发动新指令</t>
+  </si>
+  <si>
+    <t>完美</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Supervisor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>};</t>
+  </si>
+  <si>
+    <t>struct TaskEvent {</t>
+  </si>
+  <si>
+    <t>    TaskType taskType;  // Motion-DoMotion-MotionSet-GetObj; Camera-Update-Detecte-Learn  </t>
+  </si>
+  <si>
+    <t>    TaskStatus status;</t>
+  </si>
+  <si>
+    <t>    std::chrono::steady_clock::time_point timestamp;</t>
+  </si>
+  <si>
+    <t>    ResultData result;      </t>
+  </si>
+  <si>
+    <t>    std::string moduleName;  // Motion;Camera;Speaker;Nlu;Microphone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>    int taskId;   // Motion 0000-999; Camera 1000-1999; Speaker 2000-2999; Nlu 3000-3999; Microphone 4000-4999; Screen 5000-</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -880,6 +993,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -903,7 +1024,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -917,6 +1038,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -21025,6 +21149,7037 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>163284</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>27215</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>535214</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>117931</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="矩形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AE34767-8E78-406E-9640-F1543DB5497F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="772884" y="205015"/>
+          <a:ext cx="18659930" cy="7558316"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>552718</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>95304</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>163286</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>18879</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="矩形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A09E618-48CE-43B7-8BB0-96172EA271C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6648718" y="1517704"/>
+          <a:ext cx="1439368" cy="634775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Raw Frame Callback</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="矩形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3D66913-D9D1-4535-A6A0-F1A95404E846}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6851650" y="3676650"/>
+          <a:ext cx="1295400" cy="636270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>RobotBrain</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>528171</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>149786</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>604371</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>74856</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="矩形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC217A21-C15D-4E25-A574-FEBB1C4BC901}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10891371" y="2638986"/>
+          <a:ext cx="1295400" cy="636270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>CameraApp</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>542365</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>135217</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>5977</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>60287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="矩形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8117C0B-B210-4BAF-AB78-629EF3AEF818}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10905565" y="3691217"/>
+          <a:ext cx="1292412" cy="636270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MotionApp</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>537135</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>144928</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>747</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>69998</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="矩形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A7F0EB3-14B2-4532-B5EC-B4A5BD9AC627}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10900335" y="4945528"/>
+          <a:ext cx="1292412" cy="636270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SpeakerApp</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>308430</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>88901</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="矩形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48A72179-4C15-499B-8B1F-EFFE18237418}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4575630" y="3143250"/>
+          <a:ext cx="1609271" cy="636270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>ScreenApp</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(ScreenProducer)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>208643</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>90713</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>39913</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>145142</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="矩形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4FEAC32-18ED-424D-9F13-F71F93C42994}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4475843" y="4357913"/>
+          <a:ext cx="1660070" cy="765629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MicrophoneApp</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(VoiceProducer)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Vosk ASR</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>6349</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>109220</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="矩形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C0C01B9-E3D3-429E-BC4F-B341955491AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1225549" y="4451350"/>
+          <a:ext cx="1403351" cy="636270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MicrophoneEngine</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>captureThread</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>99786</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="矩形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB1DEB4D-05CE-4382-9669-030BA6BD3080}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1193800" y="3117850"/>
+          <a:ext cx="1344386" cy="636270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Screen_ui</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>UIEventCallback</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>603885</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>121285</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>508635</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>18415</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="矩形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22347780-868C-410B-820D-5A1A244FE9D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1213485" y="9011285"/>
+          <a:ext cx="1733550" cy="2564130"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>std::string type</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>std:: string data</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>type: MOTION_LEARN</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MOTION_CONFIRM</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>VISION_LEARN</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>VISION_DETECT</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>VISION_UPDATE</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>DO_MOTION</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>data: obj string</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>motion_name string</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>motion</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>99786</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>57785</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>308430</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>83185</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="直接箭头连接符 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2B7B316-4404-4BE9-9C7A-FD599EDCE70B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="11" idx="3"/>
+          <a:endCxn id="8" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2538186" y="3435985"/>
+          <a:ext cx="2037444" cy="25400"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>117928</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>208643</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>148499</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="直接箭头连接符 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5E6A736-9C80-4E16-BC8B-7ECA0D5C7011}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="10" idx="3"/>
+          <a:endCxn id="9" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2628900" y="4740728"/>
+          <a:ext cx="1846943" cy="30571"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>88901</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>83185</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="肘形连接符 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5265631-3D42-40FF-9FED-CF8520A1D4D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="3"/>
+          <a:endCxn id="4" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6184901" y="3461385"/>
+          <a:ext cx="1314449" cy="215265"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>39913</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>117928</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="肘形连接符 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D92BEC6F-8BC3-40B6-BCA5-9D6E705F4651}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="9" idx="3"/>
+          <a:endCxn id="4" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6135913" y="4312920"/>
+          <a:ext cx="1363437" cy="427808"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>210297</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>151653</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>438897</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76723</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="矩形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AA218AA-1395-4B27-8574-C9D9C1AB0E8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8744697" y="2640853"/>
+          <a:ext cx="1447800" cy="636270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>CameraTask_Thread</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>33020</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="矩形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8468E545-5941-48A0-9E82-67C1187DDE13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8839200" y="3663950"/>
+          <a:ext cx="1447800" cy="636270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:sym typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>Motion</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Task_Thread</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>218621</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>136979</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>447221</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>62049</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="矩形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9A9EF36-44A3-4119-9C30-0A3823DE17DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8753021" y="4937579"/>
+          <a:ext cx="1447800" cy="636270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:sym typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>Speaker</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Task_Thread</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>114189</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>210297</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>83185</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="肘形连接符 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DA2D5D0-34AD-4C10-B861-858886F29B93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="17" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="8147050" y="2958989"/>
+          <a:ext cx="597647" cy="1035796"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>83185</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>218621</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>99514</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="肘形连接符 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C266204-B520-4629-860C-B43237B48449}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="19" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8147050" y="3994785"/>
+          <a:ext cx="605971" cy="1260929"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>70485</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>83185</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="直接箭头连接符 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{362FC966-7F5B-4EBF-BD06-28CA11148F9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="18" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="8147050" y="3982085"/>
+          <a:ext cx="692150" cy="12700"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>191247</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>132229</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>267447</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>57299</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="矩形 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{182B7963-5B43-4B9E-A1A9-2AB4E2090FBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12992847" y="4932829"/>
+          <a:ext cx="1295400" cy="636270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SpeakerEngine</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>_synthesisThread</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>_playbackThread</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>567766</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>52292</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>31377</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>179293</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="矩形 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1728D651-4E59-49CE-B88B-B1E23004A97D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1177366" y="1652492"/>
+          <a:ext cx="1292411" cy="660401"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Cam_Capture</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>219637</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>137460</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>295837</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>61035</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="矩形 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B8A3677-9020-47D9-84D2-72435A5BC9B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13021237" y="3693460"/>
+          <a:ext cx="1295400" cy="634775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MotionManager</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>_motionworker</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>299358</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>132976</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>493060</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>56551</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="矩形 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{045E309D-0905-464A-8D7D-FDB95AE69BB4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14886215" y="3761547"/>
+          <a:ext cx="1409274" cy="649290"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>PwmBoardController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>116116</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>53148</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>192315</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>171824</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="矩形 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C070CBE3-BDB9-426E-865B-A6F3CC0E6029}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14746516" y="1653348"/>
+          <a:ext cx="1295399" cy="652076"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>CameraEngine</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>workerThread</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>246528</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>29882</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>322728</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>14941</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="矩形 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ABB97F2-6D02-4288-B946-C1566885411C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13048128" y="2696882"/>
+          <a:ext cx="1295400" cy="518459"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>CameraHandle</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>cameraThread</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>438897</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>112322</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>528171</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>114189</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="29" name="直接箭头连接符 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F527179-873C-466E-B625-C559E2546EB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="17" idx="3"/>
+          <a:endCxn id="5" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="10192497" y="2957122"/>
+          <a:ext cx="698874" cy="1867"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>70485</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>542365</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>97752</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="直接箭头连接符 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE58DA65-9B89-4037-B43C-53F2764D2FFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="18" idx="3"/>
+          <a:endCxn id="6" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10287000" y="3982085"/>
+          <a:ext cx="618565" cy="27267"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>5977</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>97752</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>219637</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>99248</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="直接箭头连接符 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2070F35F-C0B8-4D1E-A7F3-EC934227B46D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="6" idx="3"/>
+          <a:endCxn id="25" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12197977" y="4009352"/>
+          <a:ext cx="823260" cy="1496"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>295837</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>94763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>299358</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>99247</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="32" name="直接箭头连接符 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5DCF1FD-7D26-4E06-93EC-6C74531461F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="25" idx="3"/>
+          <a:endCxn id="26" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="14274908" y="4086192"/>
+          <a:ext cx="611307" cy="4484"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>447221</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>99514</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>537135</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>107463</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="直接箭头连接符 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC128F39-A28B-40AE-A019-DE5748D27D9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="19" idx="3"/>
+          <a:endCxn id="7" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10200821" y="5255714"/>
+          <a:ext cx="699514" cy="7949"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>747</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>94764</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>191247</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>107463</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="直接箭头连接符 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67440941-49A8-4AB0-8976-0201F6A2E9AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="7" idx="3"/>
+          <a:endCxn id="23" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="12192747" y="5250964"/>
+          <a:ext cx="800100" cy="12699"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>267447</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>94764</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>322731</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>112693</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="35" name="直接箭头连接符 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2375CBD6-A5D7-490E-88F3-2DC60C0CD45A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="23" idx="3"/>
+          <a:endCxn id="36" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14288247" y="5250964"/>
+          <a:ext cx="2493684" cy="17929"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>322731</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>150905</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>398930</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>74480</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="矩形 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A477F15-0B53-4B25-9A9E-EDB1B250E2A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16781931" y="4951505"/>
+          <a:ext cx="1295399" cy="634775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Audio Output</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>speaker</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>322731</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>128494</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>398930</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>52069</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="矩形 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6830551-EC38-4313-9856-73EB7B0BE0A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16781931" y="3684494"/>
+          <a:ext cx="1295399" cy="634775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Motor Output</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Servo</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>500530</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>112694</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>330202</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>117176</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="38" name="直接箭头连接符 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{594A5A54-6F09-4CD0-8E1E-4FB3F927C5A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="16350130" y="4024294"/>
+          <a:ext cx="439272" cy="4482"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>370544</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>131483</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>446743</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>55057</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="矩形 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8925DFA-8D0E-426D-A9D4-0C876FBBDF34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16829744" y="2620683"/>
+          <a:ext cx="1295399" cy="634774"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Detection Output</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Screen</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>26892</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>101919</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>172356</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>68823</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="矩形 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF269581-C182-4699-8E63-59081C82A20E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15266892" y="2235519"/>
+          <a:ext cx="1364664" cy="500304"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Detection Result Data</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>31377</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>21772</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>116116</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>25079</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="41" name="直接箭头连接符 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90A50014-3D50-484C-881C-085F6AED4344}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="24" idx="3"/>
+          <a:endCxn id="27" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2469777" y="1977572"/>
+          <a:ext cx="12276739" cy="3307"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>192315</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>21772</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>408644</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>131483</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="肘形连接符 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{555A6A44-FD11-4F5E-AFC4-DAF9022EDEF2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="27" idx="3"/>
+          <a:endCxn id="39" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16041915" y="1977572"/>
+          <a:ext cx="1435529" cy="643111"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>543431</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>36393</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>54430</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="矩形 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAEA9612-C119-4F32-8487-F422B55243AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13345031" y="1636593"/>
+          <a:ext cx="1339799" cy="455279"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Raw Image Data</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>604371</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>246528</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>112322</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="44" name="直接箭头连接符 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{389F2BA4-399D-4ABE-A826-BD4D4B61580F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="5" idx="3"/>
+          <a:endCxn id="28" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="12186771" y="2956859"/>
+          <a:ext cx="861357" cy="263"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>119530</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>70222</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>431052</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>37127</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="矩形 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1512B4F4-FD97-45D1-B2E6-93DE6F8C6437}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14749930" y="4870822"/>
+          <a:ext cx="1530722" cy="500305"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Sherpa TTS Processing</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>322728</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>171824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>154216</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>113126</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="46" name="肘形连接符 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE6A99D4-3C1A-4321-A756-FC024C71B5B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="28" idx="3"/>
+          <a:endCxn id="27" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="14343528" y="2305424"/>
+          <a:ext cx="1050688" cy="652502"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>242795</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>172673</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>81643</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>63498</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="矩形 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1047E7D2-D1FA-4B8A-A387-2E5BFF56E46B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14263595" y="2839673"/>
+          <a:ext cx="1667648" cy="602025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Deepdiff</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Image detect and feature managment</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>251865</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>100106</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>181429</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>67010</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="矩形 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AFDBE92-C476-44B6-9D07-4D2A1F0D44C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17320665" y="2055906"/>
+          <a:ext cx="1148764" cy="500304"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>LVGL Display</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>549407</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>253999</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>137766</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="矩形 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40DA1E67-A9C5-4332-A7CD-6CE9C63685CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12131807" y="2197100"/>
+          <a:ext cx="923792" cy="785466"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Vision-related Commands</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>574807</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>150905</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>290286</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>117809</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="矩形 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19B3ED3C-B749-43AC-A42C-6EFADA1E758D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12157207" y="3529105"/>
+          <a:ext cx="934679" cy="500304"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Motion Commands</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>536707</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>149091</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>317499</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>115995</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="矩形 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5561226A-6DB3-4E0F-93C3-2560D2244CFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12119107" y="4771891"/>
+          <a:ext cx="999992" cy="500304"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Speech Commands</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>326571</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>45358</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>353786</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>172358</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="矩形 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44268C0E-3021-46F5-AB81-3B641E03D5E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="936171" y="1289958"/>
+          <a:ext cx="1856015" cy="5461000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>116114</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>97973</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>217715</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="矩形 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00DB08C8-0670-4026-879F-AA6BE3D814F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16575314" y="1164773"/>
+          <a:ext cx="1930401" cy="5577113"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="00B0F0"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>478971</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>54429</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>52615</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="矩形 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9431E1AB-9F7E-4000-9721-0ABEABFFE94C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1088571" y="5921829"/>
+          <a:ext cx="1476829" cy="531586"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Input</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>377371</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>34472</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>32658</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="矩形 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CF1C05F-D2CF-459D-9F23-3112026595F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16836571" y="5901872"/>
+          <a:ext cx="1476829" cy="531586"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="00B0F0"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Output</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>61046</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>180350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="矩形 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7F9A12C-9D46-464C-90F5-20C864E01A22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3109046" y="3104243"/>
+          <a:ext cx="1437554" cy="454307"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>22947</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>90714</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>553358</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>172359</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="矩形 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3939C08A-860C-42A8-9319-8092A0D17AD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3070947" y="4357914"/>
+          <a:ext cx="1140011" cy="437245"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>AudioCallback</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>195304</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>154215</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>226785</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="矩形 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12AC466A-85CF-45A0-985D-71D29D662C8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6291304" y="2999015"/>
+          <a:ext cx="1250681" cy="442685"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Trigger Callback: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>handleUISignal</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>592633</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>127001</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>217714</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76936</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="59" name="矩形 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D9FF6EA-55AB-490A-A64E-11C27B77C8FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6688633" y="4749801"/>
+          <a:ext cx="1453881" cy="483335"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Trigger Callback: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>handleIncomingText</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>453571</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>90715</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>299357</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>27215</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="矩形 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07C70475-5F5E-4A9C-8E5F-2F106EA44A73}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2891971" y="2579915"/>
+          <a:ext cx="5332186" cy="3670300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>359228</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>170544</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>7257</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>168730</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="61" name="矩形 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{157B8763-5A43-40CD-BC17-94D388E41C0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4626428" y="5504544"/>
+          <a:ext cx="1476829" cy="531586"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Brain</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>426358</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>9072</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>90713</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="62" name="矩形 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9BED96C-9C27-477A-91BB-D9495E27BFC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8351158" y="1531257"/>
+          <a:ext cx="8117114" cy="4782456"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="92D050"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>466270</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>177801</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>114299</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>175988</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="矩形 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF4D0A01-8326-49EF-8F84-E928D931D5F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12048670" y="5689601"/>
+          <a:ext cx="1476829" cy="531587"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="92D050"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Executor</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>417285</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>36286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>90713</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>34472</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="矩形 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D7592DC-6CC7-4A34-99EC-27B2B3448DD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8951685" y="6970486"/>
+          <a:ext cx="2721428" cy="531586"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>CogniArm  V3.0</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>102776</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>70757</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>25401</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>152402</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="矩形 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A7DCF16-52A4-4C7B-9E1F-BB250AE3D220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3150776" y="3093357"/>
+          <a:ext cx="1141825" cy="437245"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>UISignalCallback</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>254002</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>108856</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="66" name="矩形 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9970D6DA-47CB-4ADB-AF7A-8534861EF726}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16967200" y="382814"/>
+          <a:ext cx="2184402" cy="615042"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1600">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Callback</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1600">
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Thread</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1600">
+            <a:solidFill>
+              <a:srgbClr val="92D050"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -21711,6 +28866,550 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FBE6CEE-E60D-4013-8E20-4E65D4F7F6C9}">
+  <dimension ref="B2:AB52"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H2" t="s">
+        <v>129</v>
+      </c>
+      <c r="L2" t="s">
+        <v>130</v>
+      </c>
+      <c r="T2" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H6" t="s">
+        <v>137</v>
+      </c>
+      <c r="L6" t="s">
+        <v>138</v>
+      </c>
+      <c r="T6" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z6">
+        <v>3</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L7" t="s">
+        <v>140</v>
+      </c>
+      <c r="T7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>142</v>
+      </c>
+      <c r="T8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F11" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z12">
+        <v>3</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L16" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="T16" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F17" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z17">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="L20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="H21" s="3"/>
+      <c r="L21" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="T21" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="L24" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="L26" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="T26" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L27" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F30" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z30">
+        <v>2</v>
+      </c>
+      <c r="AB30" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="L31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="L33" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="T33" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F35" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z35">
+        <v>2</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B37" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="T39" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L40" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="T40" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L41" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B44" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B47" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B48" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F9A8F03-984C-4274-A8CF-5C5DF0B4E628}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D00BA4E-D801-4B22-92DF-4E1CBD55A910}">
+  <dimension ref="B52"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C45D017E-1C2F-472A-B6B5-E4BAB0948980}">
+  <dimension ref="B2:B11"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
@@ -22039,7 +29738,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A2:G115"/>
+  <dimension ref="A2:G141"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -22367,7 +30066,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>122</v>
       </c>
@@ -22378,9 +30077,104 @@
         <v>124</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B119" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B120" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B121" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B122" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B123" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B124" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B125" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B126" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B128" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B137" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B141" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Project_Planning/overall.xlsx
+++ b/docs/Project_Planning/overall.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Git_doc\Real-Time-Embedded-Programming\docs\Project_Planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE62A17F-E570-4B54-AA78-FDBF9687A702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B93ACF-0B2E-4F53-AEF8-871E9CF1E081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="992" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="992" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="1" r:id="rId1"/>
@@ -23,9 +23,9 @@
     <sheet name="data" sheetId="13" r:id="rId8"/>
     <sheet name="线程管理_0409" sheetId="14" r:id="rId9"/>
     <sheet name="线程管理_0409 _eng" sheetId="15" r:id="rId10"/>
-    <sheet name="线程管理_0411" sheetId="16" r:id="rId11"/>
-    <sheet name="生命周期控制" sheetId="17" r:id="rId12"/>
-    <sheet name="data (2)" sheetId="18" r:id="rId13"/>
+    <sheet name="Thread_Manager_04020 _eng" sheetId="20" r:id="rId11"/>
+    <sheet name="线程管理_0411" sheetId="16" r:id="rId12"/>
+    <sheet name="生命周期控制" sheetId="17" r:id="rId13"/>
     <sheet name="Sheet2" sheetId="19" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="280">
   <si>
     <t>Motion学习方面如何配置？</t>
   </si>
@@ -949,6 +949,68 @@
   <si>
     <t>    int taskId;   // Motion 0000-999; Camera 1000-1999; Speaker 2000-2999; Nlu 3000-3999; Microphone 4000-4999; Screen 5000-</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">voskThread </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MicrophoneApp.cpp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VoiceProducer:start_thread()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VoiceProducer:stop_thread()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RobotSystem::stop()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pinThreadToCore(voskThread, "VoskWorkThread", 3);</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microphone vosk</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All threads are initialized after the system structure is constructed and are bound to specific CPU cores. See `cogniArm.cpp` → `start_thread()` for implementation details.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Task(Executor)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpeakerExecutor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MotionExecutor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CameraExecutor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This thread assists executor modules in receiving tasks.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Depending on the core assigned to the corresponding executor module.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pinThreadToCore(_TaskWorker,"Supervisor",core);</t>
+  </si>
+  <si>
+    <t>_TaskWorker</t>
   </si>
 </sst>
 </file>
@@ -14123,15 +14185,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>163284</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>27215</xdr:rowOff>
+      <xdr:colOff>163283</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>23090</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>535214</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>117931</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>588817</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>99785</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -14146,8 +14208,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="771070" y="208644"/>
-          <a:ext cx="18605501" cy="7710716"/>
+          <a:off x="775192" y="1581726"/>
+          <a:ext cx="21230443" cy="7696695"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14187,13 +14249,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>552718</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>95304</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>163286</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>18879</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -14263,13 +14325,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>146050</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>222250</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -14436,13 +14498,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>528171</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>149786</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>604371</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>74856</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -14609,13 +14671,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>542365</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>135217</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>5977</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>60287</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -14782,13 +14844,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>537135</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>144928</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>747</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>69998</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -14955,13 +15017,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>308430</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>88901</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -15139,14 +15201,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>208643</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>90713</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>39913</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>145142</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>92364</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -15161,8 +15223,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4463143" y="4444999"/>
-          <a:ext cx="1654627" cy="780143"/>
+          <a:off x="4492007" y="5459349"/>
+          <a:ext cx="1666997" cy="867560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15323,6 +15385,33 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>voskWorker</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>Vosk ASR</a:t>
           </a:r>
         </a:p>
@@ -15334,13 +15423,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>6349</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>109220</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -15534,13 +15623,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>584200</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>99786</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>20320</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -15734,13 +15823,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>603885</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>121285</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>508635</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>18415</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -16033,13 +16122,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>99786</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>57785</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>308430</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>83185</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16092,14 +16181,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>117928</xdr:rowOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>144376</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>208643</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>148499</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>4947</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -16117,9 +16206,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2621643" y="4835071"/>
-          <a:ext cx="1841500" cy="30571"/>
+        <a:xfrm>
+          <a:off x="2638136" y="5859376"/>
+          <a:ext cx="1853871" cy="33753"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -16152,13 +16241,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>88901</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>83185</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>120650</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16211,14 +16300,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>39913</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>117928</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>4947</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -16236,8 +16325,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="6117770" y="4400006"/>
-          <a:ext cx="1359809" cy="435065"/>
+          <a:off x="6159004" y="5414356"/>
+          <a:ext cx="1368055" cy="478773"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector2">
           <a:avLst/>
@@ -16270,13 +16359,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>210297</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>151653</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>438897</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>76723</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -16442,15 +16531,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:colOff>200891</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>119496</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>33020</xdr:rowOff>
+      <xdr:colOff>429491</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>44566</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -16465,8 +16554,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8229600" y="2241550"/>
-          <a:ext cx="1447800" cy="636270"/>
+          <a:off x="8767618" y="4795405"/>
+          <a:ext cx="1452418" cy="617797"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16625,13 +16714,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>218621</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>136979</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>447221</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>62049</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -16807,13 +16896,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>222250</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>114189</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>210297</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>83185</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16868,13 +16957,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>222250</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>83185</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>218621</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>99514</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16929,13 +17018,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>222250</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>70485</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>82031</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:colOff>200891</xdr:colOff>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>83185</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16954,8 +17043,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="7537450" y="2559685"/>
-          <a:ext cx="692150" cy="12700"/>
+          <a:off x="8177068" y="5104304"/>
+          <a:ext cx="590550" cy="1154"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -16988,13 +17077,13 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>191247</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>132229</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>267447</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>57299</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -17215,13 +17304,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>567766</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>52292</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>31377</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>179293</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -17388,13 +17477,13 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>219637</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>137460</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>295837</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>61035</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -17561,13 +17650,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>416860</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>132976</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>493059</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>56551</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -17761,13 +17850,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>116116</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>53148</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>192315</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>171824</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -17961,13 +18050,13 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>246528</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>29882</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>322728</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>14941</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -18161,13 +18250,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>438897</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>112322</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>528171</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>114189</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -18219,14 +18308,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>70485</xdr:rowOff>
+      <xdr:colOff>429491</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>82031</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>542365</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>97752</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -18245,8 +18334,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9722224" y="3297779"/>
-          <a:ext cx="621553" cy="27267"/>
+          <a:off x="10220036" y="5104304"/>
+          <a:ext cx="724784" cy="15721"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -18279,13 +18368,13 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>5977</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>97752</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>219637</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>99248</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -18338,13 +18427,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>295837</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>94764</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>416860</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>99248</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -18397,13 +18486,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>447221</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>99514</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>537135</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>107463</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -18456,13 +18545,13 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>747</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>94764</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>191247</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>107463</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -18515,13 +18604,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>267447</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>94764</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>322731</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>112693</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -18574,13 +18663,13 @@
     <xdr:from>
       <xdr:col>27</xdr:col>
       <xdr:colOff>322731</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>150905</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>398930</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>74480</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -18758,13 +18847,13 @@
     <xdr:from>
       <xdr:col>27</xdr:col>
       <xdr:colOff>322731</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>128494</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>398930</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>52069</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -18942,13 +19031,13 @@
     <xdr:from>
       <xdr:col>26</xdr:col>
       <xdr:colOff>500530</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>112694</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>330202</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>117176</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -18998,13 +19087,13 @@
     <xdr:from>
       <xdr:col>27</xdr:col>
       <xdr:colOff>370544</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>131483</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>446743</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>55057</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -19182,13 +19271,13 @@
     <xdr:from>
       <xdr:col>25</xdr:col>
       <xdr:colOff>26892</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>101919</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>172356</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>68823</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -19258,13 +19347,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>31377</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>21772</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>116116</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>25079</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -19317,13 +19406,13 @@
     <xdr:from>
       <xdr:col>26</xdr:col>
       <xdr:colOff>192315</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>21772</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>408644</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>131483</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -19376,13 +19465,13 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>543431</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>36393</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>54430</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>136072</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -19452,13 +19541,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>604371</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>112059</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>246528</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>112322</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -19511,13 +19600,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>119530</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>70222</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>431052</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>37127</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -19587,13 +19676,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>322728</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>171824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>154216</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>113126</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -19646,13 +19735,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>242795</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>172673</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>81643</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>63498</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -19725,13 +19814,13 @@
     <xdr:from>
       <xdr:col>28</xdr:col>
       <xdr:colOff>251865</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>100106</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>181429</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>67010</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -19801,13 +19890,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>549407</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>253999</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>137766</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -19877,13 +19966,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>574807</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>150905</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>290286</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>117809</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -19953,13 +20042,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>536707</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>149091</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>317499</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>115995</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -20029,13 +20118,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>326571</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>45358</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>353786</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>172358</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -20095,13 +20184,13 @@
     <xdr:from>
       <xdr:col>27</xdr:col>
       <xdr:colOff>116114</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>97973</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>217715</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>163286</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -20117,8 +20206,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16526328" y="1186544"/>
-          <a:ext cx="1924958" cy="5689599"/>
+          <a:off x="16637659" y="1137064"/>
+          <a:ext cx="1937329" cy="5433949"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -20161,13 +20250,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>478971</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>54429</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>52615</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -20223,7 +20312,7 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Input</a:t>
+            <a:t>producer</a:t>
           </a:r>
           <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
             <a:solidFill>
@@ -20239,13 +20328,13 @@
     <xdr:from>
       <xdr:col>27</xdr:col>
       <xdr:colOff>377371</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>34472</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>32658</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -20317,13 +20406,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>61046</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>81643</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>180350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -20385,13 +20474,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>22947</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>90714</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>553358</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>172359</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -20461,13 +20550,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>195304</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>154215</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>226785</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -20540,13 +20629,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>592633</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>127001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>217714</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>76936</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -20619,13 +20708,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>453571</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>90715</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>299357</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>27215</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -20685,13 +20774,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>359228</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>170544</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>7257</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>168730</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -20763,14 +20852,14 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>426358</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>108857</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>9072</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>90713</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>92364</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -20785,8 +20874,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8327572" y="1560286"/>
-          <a:ext cx="8091714" cy="4880427"/>
+          <a:off x="8381176" y="2706584"/>
+          <a:ext cx="8149441" cy="5005780"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -20828,15 +20917,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>466270</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>177801</xdr:rowOff>
+      <xdr:colOff>385452</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>62346</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>114299</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>175988</xdr:rowOff>
+      <xdr:colOff>33481</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>60534</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -20851,8 +20940,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12014199" y="5802087"/>
-          <a:ext cx="1471386" cy="542472"/>
+          <a:off x="12011725" y="6989619"/>
+          <a:ext cx="1483756" cy="517733"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -20907,13 +20996,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>417285</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>36286</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>90713</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>34472</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -20969,7 +21058,7 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>CogniArm  V2.0</a:t>
+            <a:t>CogniArm  V3.0</a:t>
           </a:r>
           <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
             <a:solidFill>
@@ -20985,13 +21074,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>102776</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>70757</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>25401</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>152402</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -21059,16 +21148,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>27214</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>217715</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>137720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>254002</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>108856</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>575625</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>46180</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -21083,8 +21172,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16918214" y="390071"/>
-          <a:ext cx="2177145" cy="625928"/>
+          <a:off x="3277260" y="1696356"/>
+          <a:ext cx="2193638" cy="601188"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -21146,30 +21235,25 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>163284</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>27215</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>522515</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>23091</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>535214</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>117931</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>577273</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="矩形 1">
+        <xdr:cNvPr id="15" name="矩形 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AE34767-8E78-406E-9640-F1543DB5497F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45952ABD-B92E-453B-AED2-773872894D06}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21177,15 +21261,18 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="772884" y="205015"/>
-          <a:ext cx="18659930" cy="7558316"/>
+          <a:off x="18879788" y="1928091"/>
+          <a:ext cx="2502394" cy="5865090"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -21216,23 +21303,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>552718</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>95304</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>425860</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>86261</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>163286</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>18879</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>126998</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>80817</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="矩形 2">
+        <xdr:cNvPr id="29" name="矩形 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A09E618-48CE-43B7-8BB0-96172EA271C1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81823E7E-3611-4D90-A063-8315C36A80F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21240,47 +21327,49 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6648718" y="1517704"/>
-          <a:ext cx="1439368" cy="634775"/>
+          <a:off x="19395042" y="7013534"/>
+          <a:ext cx="1536865" cy="514101"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
           <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
+            <a:shade val="15000"/>
           </a:schemeClr>
         </a:lnRef>
         <a:fillRef idx="1">
           <a:schemeClr val="accent1"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
+          <a:schemeClr val="accent1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+            <a:rPr lang="en-US" altLang="zh-CN" sz="2000">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Raw Frame Callback</a:t>
+            <a:t>Supervisor</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -21292,23 +21381,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>146050</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>422837</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>88697</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>222250</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>57726</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="矩形 3">
+        <xdr:cNvPr id="31" name="矩形 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3D66913-D9D1-4535-A6A0-F1A95404E846}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBCEE8F0-1E17-4872-A374-BA6A268B21F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21316,8 +21405,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6851650" y="3676650"/>
-          <a:ext cx="1295400" cy="636270"/>
+          <a:off x="19392019" y="2340061"/>
+          <a:ext cx="1470616" cy="430848"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -21451,13 +21540,32 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
-            <a:t>RobotBrain</a:t>
+            <a:t>General</a:t>
           </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> Task detail</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -21465,23 +21573,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>528171</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>149786</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>427182</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>150090</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>604371</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>74856</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>115455</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>103909</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="矩形 4">
+        <xdr:cNvPr id="32" name="矩形 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC217A21-C15D-4E25-A574-FEBB1C4BC901}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03B79828-4FB8-437F-B90D-999B49E78410}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21489,8 +21597,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10891371" y="2638986"/>
-          <a:ext cx="1295400" cy="636270"/>
+          <a:off x="19396364" y="6038272"/>
+          <a:ext cx="1524000" cy="646546"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -21624,12 +21732,29 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
-            <a:t>CameraApp</a:t>
+            <a:t>System delay record</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>(_processLoop)</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -21638,23 +21763,85 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>542365</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>135217</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>115455</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>5977</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>60287</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>138545</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>130876</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="53" name="肘形连接符 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1E17860-91A7-4AE3-87F8-78FA8E930849}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="32" idx="3"/>
+          <a:endCxn id="62" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20920364" y="6361545"/>
+          <a:ext cx="634999" cy="2255240"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 136000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>300181</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>7752</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>138545</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>80817</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="矩形 5">
+        <xdr:cNvPr id="62" name="矩形 61">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8117C0B-B210-4BAF-AB78-629EF3AEF818}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F03980D8-8937-4E63-BE5C-8597AEC835E0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21662,8 +21849,218 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10905565" y="3691217"/>
-          <a:ext cx="1292412" cy="636270"/>
+          <a:off x="19881272" y="8147297"/>
+          <a:ext cx="1674091" cy="938975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>External test folder</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>326736</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>88696</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>546236</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>57726</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="79" name="肘形连接符 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED551654-34BD-4C21-B77C-4BD3941A828B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="31" idx="0"/>
+          <a:endCxn id="98" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1" flipV="1">
+          <a:off x="14312289" y="-2466857"/>
+          <a:ext cx="1008121" cy="10621955"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -22676"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>99290</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>57727</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>554181</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>138546</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="98" name="矩形 97">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77820539-7DAF-482A-B574-31B2092B7ED9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8666017" y="3348182"/>
+          <a:ext cx="1678709" cy="4237182"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="92D050"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>236478</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>461817</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>23091</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="99" name="矩形 98">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0642D18E-3F88-40A9-9E89-A0DF07174834}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8803205" y="6927273"/>
+          <a:ext cx="1449157" cy="542636"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -21797,12 +22194,12 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>MotionApp</a:t>
+            <a:t>General Task queue</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -21811,23 +22208,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>537135</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>144928</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>538968</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>83127</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>747</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>69998</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>152398</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>106217</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="矩形 6">
+        <xdr:cNvPr id="103" name="矩形 102">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A7F0EB3-14B2-4532-B5EC-B4A5BD9AC627}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54EA20EA-7494-4703-A849-393128AA1805}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21835,19 +22232,15 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10900335" y="4945528"/>
-          <a:ext cx="1292412" cy="636270"/>
+          <a:off x="13389059" y="1641763"/>
+          <a:ext cx="1449157" cy="542636"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
+        <a:noFill/>
         <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
+          <a:noFill/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -21970,12 +22363,12 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>SpeakerApp</a:t>
+            <a:t>Task Feedback</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -21984,1113 +22377,35 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>308430</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>546236</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>88901</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="矩形 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48A72179-4C15-499B-8B1F-EFFE18237418}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4575630" y="3143250"/>
-          <a:ext cx="1609271" cy="636270"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>ScreenApp</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(ScreenProducer)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>208643</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>90713</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>39913</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>145142</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="矩形 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4FEAC32-18ED-424D-9F13-F71F93C42994}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4475843" y="4357913"/>
-          <a:ext cx="1660070" cy="765629"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>MicrophoneApp</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(VoiceProducer)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Vosk ASR</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>6349</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>109220</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="矩形 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C0C01B9-E3D3-429E-BC4F-B341955491AC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1225549" y="4451350"/>
-          <a:ext cx="1403351" cy="636270"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>MicrophoneEngine</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>captureThread</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>584200</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>99786</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>20320</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="矩形 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB1DEB4D-05CE-4382-9669-030BA6BD3080}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1193800" y="3117850"/>
-          <a:ext cx="1344386" cy="636270"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Screen_ui</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>UIEventCallback</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>603885</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>121285</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>508635</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>18415</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="矩形 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22347780-868C-410B-820D-5A1A244FE9D4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1213485" y="9011285"/>
-          <a:ext cx="1733550" cy="2564130"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>std::string type</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>std:: string data</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>type: MOTION_LEARN</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>MOTION_CONFIRM</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>VISION_LEARN</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>VISION_DETECT</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>VISION_UPDATE</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>DO_MOTION</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>data: obj string</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>motion_name string</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>motion</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>99786</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>57785</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>308430</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>83185</xdr:rowOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>577273</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>150090</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="13" name="直接箭头连接符 12">
+        <xdr:cNvPr id="133" name="直接箭头连接符 132">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2B7B316-4404-4BE9-9C7A-FD599EDCE70B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D389EF2-9422-4172-937B-C3F1F5CF196C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="11" idx="3"/>
-          <a:endCxn id="8" idx="1"/>
+          <a:stCxn id="32" idx="0"/>
+          <a:endCxn id="31" idx="2"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2538186" y="3435985"/>
-          <a:ext cx="2037444" cy="25400"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="20127327" y="2770909"/>
+          <a:ext cx="31037" cy="3267363"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -23121,201 +22436,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>117928</xdr:rowOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>423786</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>153078</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>208643</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>392545</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>148499</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="直接箭头连接符 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5E6A736-9C80-4E16-BC8B-7ECA0D5C7011}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:cxnSpLocks/>
-          <a:stCxn id="10" idx="3"/>
-          <a:endCxn id="9" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2628900" y="4740728"/>
-          <a:ext cx="1846943" cy="30571"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>88901</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>83185</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="15" name="肘形连接符 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5265631-3D42-40FF-9FED-CF8520A1D4D4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="8" idx="3"/>
-          <a:endCxn id="4" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6184901" y="3461385"/>
-          <a:ext cx="1314449" cy="215265"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector2">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>39913</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>117928</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="肘形连接符 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D92BEC6F-8BC3-40B6-BCA5-9D6E705F4651}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="9" idx="3"/>
-          <a:endCxn id="4" idx="2"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="6135913" y="4312920"/>
-          <a:ext cx="1363437" cy="427808"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector2">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>210297</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>151653</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>438897</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>76723</xdr:rowOff>
+      <xdr:rowOff>103910</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="矩形 16">
+        <xdr:cNvPr id="136" name="矩形 135">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AA218AA-1395-4B27-8574-C9D9C1AB0E8B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C099EC5E-87B4-452E-8EAB-B45AE083A318}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23323,2920 +22460,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8744697" y="2640853"/>
-          <a:ext cx="1447800" cy="636270"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>CameraTask_Thread</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>33020</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="矩形 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8468E545-5941-48A0-9E82-67C1187DDE13}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8839200" y="3663950"/>
-          <a:ext cx="1447800" cy="636270"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN">
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-              <a:sym typeface="+mn-ea"/>
-            </a:rPr>
-            <a:t>Motion</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Task_Thread</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>218621</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>136979</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>447221</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>62049</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="矩形 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9A9EF36-44A3-4119-9C30-0A3823DE17DF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8753021" y="4937579"/>
-          <a:ext cx="1447800" cy="636270"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN">
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-              <a:sym typeface="+mn-ea"/>
-            </a:rPr>
-            <a:t>Speaker</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Task_Thread</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>222250</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>114189</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>210297</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>83185</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="20" name="肘形连接符 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DA2D5D0-34AD-4C10-B861-858886F29B93}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="3"/>
-          <a:endCxn id="17" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="8147050" y="2958989"/>
-          <a:ext cx="597647" cy="1035796"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 50000"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>222250</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>83185</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>218621</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>99514</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="肘形连接符 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C266204-B520-4629-860C-B43237B48449}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="3"/>
-          <a:endCxn id="19" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8147050" y="3994785"/>
-          <a:ext cx="605971" cy="1260929"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 50000"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>222250</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>70485</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>83185</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="直接箭头连接符 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{362FC966-7F5B-4EBF-BD06-28CA11148F9A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="3"/>
-          <a:endCxn id="18" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="8147050" y="3982085"/>
-          <a:ext cx="692150" cy="12700"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>191247</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>132229</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>267447</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>57299</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="矩形 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{182B7963-5B43-4B9E-A1A9-2AB4E2090FBB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12992847" y="4932829"/>
-          <a:ext cx="1295400" cy="636270"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>SpeakerEngine</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>_synthesisThread</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>_playbackThread</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>567766</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>52292</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>31377</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>179293</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="矩形 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1728D651-4E59-49CE-B88B-B1E23004A97D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1177366" y="1652492"/>
-          <a:ext cx="1292411" cy="660401"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Cam_Capture</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>219637</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>137460</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>295837</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>61035</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="矩形 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B8A3677-9020-47D9-84D2-72435A5BC9B0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13021237" y="3693460"/>
-          <a:ext cx="1295400" cy="634775"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>MotionManager</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="92D050"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>_motionworker</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>299358</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>132976</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>493060</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>56551</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="矩形 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{045E309D-0905-464A-8D7D-FDB95AE69BB4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14886215" y="3761547"/>
-          <a:ext cx="1409274" cy="649290"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>PwmBoardController</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>116116</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>53148</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>192315</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>171824</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="矩形 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C070CBE3-BDB9-426E-865B-A6F3CC0E6029}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14746516" y="1653348"/>
-          <a:ext cx="1295399" cy="652076"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>CameraEngine</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>workerThread</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>246528</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>29882</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>322728</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>14941</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="矩形 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ABB97F2-6D02-4288-B946-C1566885411C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13048128" y="2696882"/>
-          <a:ext cx="1295400" cy="518459"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>CameraHandle</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>cameraThread</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>438897</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>112322</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>528171</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>114189</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="29" name="直接箭头连接符 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F527179-873C-466E-B625-C559E2546EB9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="17" idx="3"/>
-          <a:endCxn id="5" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="10192497" y="2957122"/>
-          <a:ext cx="698874" cy="1867"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>70485</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>542365</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>97752</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="30" name="直接箭头连接符 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE58DA65-9B89-4037-B43C-53F2764D2FFA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="18" idx="3"/>
-          <a:endCxn id="6" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10287000" y="3982085"/>
-          <a:ext cx="618565" cy="27267"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>5977</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>97752</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>219637</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>99248</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="31" name="直接箭头连接符 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2070F35F-C0B8-4D1E-A7F3-EC934227B46D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="6" idx="3"/>
-          <a:endCxn id="25" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12197977" y="4009352"/>
-          <a:ext cx="823260" cy="1496"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>295837</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>94763</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>299358</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>99247</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="32" name="直接箭头连接符 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5DCF1FD-7D26-4E06-93EC-6C74531461F6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="25" idx="3"/>
-          <a:endCxn id="26" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="14274908" y="4086192"/>
-          <a:ext cx="611307" cy="4484"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>447221</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>99514</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>537135</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>107463</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="直接箭头连接符 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC128F39-A28B-40AE-A019-DE5748D27D9F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="19" idx="3"/>
-          <a:endCxn id="7" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10200821" y="5255714"/>
-          <a:ext cx="699514" cy="7949"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>747</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>94764</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>191247</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>107463</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="34" name="直接箭头连接符 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67440941-49A8-4AB0-8976-0201F6A2E9AF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="7" idx="3"/>
-          <a:endCxn id="23" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="12192747" y="5250964"/>
-          <a:ext cx="800100" cy="12699"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>267447</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>94764</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>322731</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>112693</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="35" name="直接箭头连接符 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2375CBD6-A5D7-490E-88F3-2DC60C0CD45A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="23" idx="3"/>
-          <a:endCxn id="36" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14288247" y="5250964"/>
-          <a:ext cx="2493684" cy="17929"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>322731</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>150905</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>398930</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>74480</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="矩形 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A477F15-0B53-4B25-9A9E-EDB1B250E2A3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16781931" y="4951505"/>
-          <a:ext cx="1295399" cy="634775"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Audio Output</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>speaker</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>322731</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>128494</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>398930</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>52069</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="矩形 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6830551-EC38-4313-9856-73EB7B0BE0A3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16781931" y="3684494"/>
-          <a:ext cx="1295399" cy="634775"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Motor Output</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Servo</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>500530</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>112694</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>330202</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>117176</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="38" name="直接箭头连接符 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{594A5A54-6F09-4CD0-8E1E-4FB3F927C5A0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="16350130" y="4024294"/>
-          <a:ext cx="439272" cy="4482"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>370544</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>131483</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>446743</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>55057</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="矩形 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8925DFA-8D0E-426D-A9D4-0C876FBBDF34}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16829744" y="2620683"/>
-          <a:ext cx="1295399" cy="634774"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="zh-CN">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Detection Output</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Screen</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>26892</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>101919</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>172356</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>68823</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="矩形 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF269581-C182-4699-8E63-59081C82A20E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15266892" y="2235519"/>
-          <a:ext cx="1364664" cy="500304"/>
+          <a:off x="20004877" y="4136260"/>
+          <a:ext cx="1192577" cy="470377"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -26273,1903 +22498,19 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Detection Result Data</a:t>
+            <a:t>Task</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> detail</a:t>
           </a:r>
           <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>31377</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>21772</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>116116</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>25079</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="41" name="直接箭头连接符 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90A50014-3D50-484C-881C-085F6AED4344}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="24" idx="3"/>
-          <a:endCxn id="27" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2469777" y="1977572"/>
-          <a:ext cx="12276739" cy="3307"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>192315</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>21772</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>408644</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>131483</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="42" name="肘形连接符 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{555A6A44-FD11-4F5E-AFC4-DAF9022EDEF2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="27" idx="3"/>
-          <a:endCxn id="39" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16041915" y="1977572"/>
-          <a:ext cx="1435529" cy="643111"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector2">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>543431</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>36393</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>54430</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>136072</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="矩形 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAEA9612-C119-4F32-8487-F422B55243AE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13345031" y="1636593"/>
-          <a:ext cx="1339799" cy="455279"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Raw Image Data</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>604371</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>112059</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>246528</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>112322</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="44" name="直接箭头连接符 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{389F2BA4-399D-4ABE-A826-BD4D4B61580F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="5" idx="3"/>
-          <a:endCxn id="28" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="12186771" y="2956859"/>
-          <a:ext cx="861357" cy="263"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>119530</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>70222</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>431052</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>37127</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="矩形 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1512B4F4-FD97-45D1-B2E6-93DE6F8C6437}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14749930" y="4870822"/>
-          <a:ext cx="1530722" cy="500305"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Sherpa TTS Processing</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>322728</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>171824</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>154216</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>113126</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="46" name="肘形连接符 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE6A99D4-3C1A-4321-A756-FC024C71B5B0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="28" idx="3"/>
-          <a:endCxn id="27" idx="2"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="14343528" y="2305424"/>
-          <a:ext cx="1050688" cy="652502"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector2">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>242795</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>172673</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>81643</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>63498</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="矩形 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1047E7D2-D1FA-4B8A-A387-2E5BFF56E46B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14263595" y="2839673"/>
-          <a:ext cx="1667648" cy="602025"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Deepdiff</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> Image detect and feature managment</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>251865</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>100106</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>181429</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>67010</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="矩形 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AFDBE92-C476-44B6-9D07-4D2A1F0D44C3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17320665" y="2055906"/>
-          <a:ext cx="1148764" cy="500304"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>LVGL Display</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>549407</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>253999</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>137766</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="矩形 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40DA1E67-A9C5-4332-A7CD-6CE9C63685CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12131807" y="2197100"/>
-          <a:ext cx="923792" cy="785466"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Vision-related Commands</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>574807</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>150905</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>290286</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>117809</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="矩形 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19B3ED3C-B749-43AC-A42C-6EFADA1E758D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12157207" y="3529105"/>
-          <a:ext cx="934679" cy="500304"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Motion Commands</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>536707</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>149091</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>317499</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>115995</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="矩形 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5561226A-6DB3-4E0F-93C3-2560D2244CFA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12119107" y="4771891"/>
-          <a:ext cx="999992" cy="500304"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Speech Commands</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>326571</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>45358</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>353786</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>172358</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="矩形 51">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44268C0E-3021-46F5-AB81-3B641E03D5E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="936171" y="1289958"/>
-          <a:ext cx="1856015" cy="5461000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>116114</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>97973</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>217715</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="53" name="矩形 52">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00DB08C8-0670-4026-879F-AA6BE3D814F9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16575314" y="1164773"/>
-          <a:ext cx="1930401" cy="5577113"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="00B0F0"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>478971</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>54429</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>52615</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="矩形 53">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9431E1AB-9F7E-4000-9721-0ABEABFFE94C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1088571" y="5921829"/>
-          <a:ext cx="1476829" cy="531586"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="2000">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Input</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>377371</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>34472</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>32658</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="矩形 54">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CF1C05F-D2CF-459D-9F23-3112026595F0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16836571" y="5901872"/>
-          <a:ext cx="1476829" cy="531586"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="00B0F0"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="2000">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Output</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>61046</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>81643</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>180350</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="矩形 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7F9A12C-9D46-464C-90F5-20C864E01A22}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3109046" y="3104243"/>
-          <a:ext cx="1437554" cy="454307"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>22947</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>90714</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>553358</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>172359</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="57" name="矩形 56">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3939C08A-860C-42A8-9319-8092A0D17AD9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3070947" y="4357914"/>
-          <a:ext cx="1140011" cy="437245"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>AudioCallback</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
-            <a:solidFill>
-              <a:srgbClr val="7030A0"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>195304</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>154215</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>226785</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="58" name="矩形 57">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12AC466A-85CF-45A0-985D-71D29D662C8E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6291304" y="2999015"/>
-          <a:ext cx="1250681" cy="442685"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Trigger Callback: </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>handleUISignal</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>592633</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>127001</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>217714</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>76936</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="59" name="矩形 58">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D9FF6EA-55AB-490A-A64E-11C27B77C8FF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6688633" y="4749801"/>
-          <a:ext cx="1453881" cy="483335"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Trigger Callback: </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>handleIncomingText</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>453571</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>90715</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>299357</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>27215</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="60" name="矩形 59">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07C70475-5F5E-4A9C-8E5F-2F106EA44A73}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2891971" y="2579915"/>
-          <a:ext cx="5332186" cy="3670300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FFC000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>359228</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>170544</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>7257</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>168730</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="61" name="矩形 60">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{157B8763-5A43-40CD-BC17-94D388E41C0E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4626428" y="5504544"/>
-          <a:ext cx="1476829" cy="531586"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FFC000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="2000">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Brain</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>426358</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>9072</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>90713</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="62" name="矩形 61">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9BED96C-9C27-477A-91BB-D9495E27BFC9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8351158" y="1531257"/>
-          <a:ext cx="8117114" cy="4782456"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="92D050"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>466270</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>177801</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>114299</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>175988</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="63" name="矩形 62">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF4D0A01-8326-49EF-8F84-E928D931D5F0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12048670" y="5689601"/>
-          <a:ext cx="1476829" cy="531587"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="92D050"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="2000">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Executor</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>417285</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>36286</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>90713</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>34472</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="64" name="矩形 63">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D7592DC-6CC7-4A34-99EC-27B2B3448DD6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8951685" y="6970486"/>
-          <a:ext cx="2721428" cy="531586"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="2000">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>CogniArm  V3.0</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>102776</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>70757</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>25401</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>152402</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="65" name="矩形 64">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A7DCF16-52A4-4C7B-9E1F-BB250AE3D220}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3150776" y="3093357"/>
-          <a:ext cx="1141825" cy="437245"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>UISignalCallback</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
-            <a:solidFill>
-              <a:srgbClr val="7030A0"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>27214</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>254002</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>108856</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="66" name="矩形 65">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9970D6DA-47CB-4ADB-AF7A-8534861EF726}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16967200" y="382814"/>
-          <a:ext cx="2184402" cy="615042"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1600">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Callback</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1600">
-              <a:solidFill>
-                <a:srgbClr val="92D050"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Thread</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1600">
-            <a:solidFill>
-              <a:srgbClr val="92D050"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -28867,6 +23208,526 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9CC65A-620D-4153-A2FB-DADD6B3AE352}">
+  <dimension ref="B2:AB61"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H6" t="s">
+        <v>137</v>
+      </c>
+      <c r="L6" t="s">
+        <v>138</v>
+      </c>
+      <c r="T6" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z6">
+        <v>3</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="L7" t="s">
+        <v>140</v>
+      </c>
+      <c r="T7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>142</v>
+      </c>
+      <c r="T8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="Z10">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L11" t="s">
+        <v>142</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F15" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z16">
+        <v>3</v>
+      </c>
+      <c r="AB16" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L20" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="T20" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z21">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="L24" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="H25" s="3"/>
+      <c r="L25" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="T25" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B27" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z27">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="L28" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B30" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="L30" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="T30" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L31" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F34" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z34">
+        <v>2</v>
+      </c>
+      <c r="AB34" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="L35" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B37" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="L37" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="T37" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F39" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="T39" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z39">
+        <v>2</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="T40" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B43" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L44" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="T44" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L45" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B47" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B48" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="49" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L49" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="Z49" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="50" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F50" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="51" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F51" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="52" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F52" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="54" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B54" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="56" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>279</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="T56" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="61" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B61" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FBE6CEE-E60D-4013-8E20-4E65D4F7F6C9}">
   <dimension ref="B2:AB52"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -29327,30 +24188,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F9A8F03-984C-4274-A8CF-5C5DF0B4E628}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D00BA4E-D801-4B22-92DF-4E1CBD55A910}">
-  <dimension ref="B52"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
-        <v>126</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30186,11 +25030,17 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B52"/>
+  <dimension ref="B20:AM59"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
+    <row r="20" spans="38:39" x14ac:dyDescent="0.25">
+      <c r="AL20" s="3"/>
+    </row>
+    <row r="31" spans="38:39" x14ac:dyDescent="0.25">
+      <c r="AM31" s="3"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
         <v>126</v>
       </c>
     </row>
